--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_e_rezmat_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_e_rezmat_a_2021_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:46</t>
+    <t xml:space="preserve">2026-09-18 09:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_e_rezmat_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_e_rezmat_a_2021_nacional.xlsx
@@ -9,15 +9,16 @@
     <sheet name="Sexo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Edad" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Nivel" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Edad'!$A$1:$C$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Nivel'!$A$1:$C$22</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t xml:space="preserve">Año</t>
   </si>
@@ -40,7 +41,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:06</t>
+    <t xml:space="preserve">2026-09-28 23:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -80,6 +81,18 @@
   </si>
   <si>
     <t xml:space="preserve">6 a 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivel educativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Básica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media humanista-científica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media técnico-profesional</t>
   </si>
 </sst>
 </file>
@@ -949,4 +962,263 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>9.95</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>9.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>9.85</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>9.88</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>9.69</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>9.56</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>5.82</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C22"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>